--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-09T00:29:47+00:00</t>
+          <t>2026-05-10T00:27:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-10T00:27:07+00:00</t>
+          <t>2026-05-11T00:27:35+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-11T00:27:35+00:00</t>
+          <t>2026-05-12T00:28:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-12T00:28:04+00:00</t>
+          <t>2026-05-13T00:30:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-13T00:30:36+00:00</t>
+          <t>2026-05-14T00:31:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-14T00:31:33+00:00</t>
+          <t>2026-05-15T00:29:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-15T00:29:11+00:00</t>
+          <t>2026-05-16T00:27:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-16T00:27:50+00:00</t>
+          <t>2026-05-17T00:28:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-17T00:28:42+00:00</t>
+          <t>2026-05-18T00:29:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-18T00:29:16+00:00</t>
+          <t>2026-05-19T00:32:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-19T00:32:42+00:00</t>
+          <t>2026-05-20T00:34:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-20T00:34:17+00:00</t>
+          <t>2026-05-21T00:35:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-21T00:35:05+00:00</t>
+          <t>2026-05-22T00:32:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-22T00:32:26+00:00</t>
+          <t>2026-05-23T00:33:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-23T00:33:15+00:00</t>
+          <t>2026-05-24T00:31:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-24T00:31:52+00:00</t>
+          <t>2026-05-25T00:34:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-25T00:34:12+00:00</t>
+          <t>2026-05-26T00:33:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-26T00:33:56+00:00</t>
+          <t>2026-05-27T00:33:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-27T00:33:50+00:00</t>
+          <t>2026-05-28T00:30:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-28T00:30:21+00:00</t>
+          <t>2026-05-29T00:36:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-29T00:36:29+00:00</t>
+          <t>2026-05-30T00:32:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-30T00:32:56+00:00</t>
+          <t>2026-05-31T00:34:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-05-31T00:34:10+00:00</t>
+          <t>2026-06-01T00:36:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-01T00:36:48+00:00</t>
+          <t>2026-06-02T00:40:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-02T00:40:34+00:00</t>
+          <t>2026-06-03T00:45:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-03T00:45:36+00:00</t>
+          <t>2026-06-04T00:43:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-04T00:43:34+00:00</t>
+          <t>2026-06-05T00:36:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-05T00:36:47+00:00</t>
+          <t>2026-06-06T00:34:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-06T00:34:46+00:00</t>
+          <t>2026-06-07T00:35:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07T00:35:43+00:00</t>
+          <t>2026-06-08T00:37:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-08T00:37:18+00:00</t>
+          <t>2026-06-09T00:32:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-09T00:32:27+00:00</t>
+          <t>2026-06-10T00:38:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-10T00:38:22+00:00</t>
+          <t>2026-06-11T00:42:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-11T00:42:37+00:00</t>
+          <t>2026-06-12T00:47:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-12T00:47:31+00:00</t>
+          <t>2026-06-13T00:39:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-13T00:39:23+00:00</t>
+          <t>2026-06-14T00:38:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-14T00:38:01+00:00</t>
+          <t>2026-06-15T00:39:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-15T00:39:23+00:00</t>
+          <t>2026-06-16T00:50:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-16T00:50:00+00:00</t>
+          <t>2026-06-17T00:39:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-17T00:39:59+00:00</t>
+          <t>2026-06-18T00:44:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-18T00:44:03+00:00</t>
+          <t>2026-06-19T00:44:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-19T00:44:03+00:00</t>
+          <t>2026-06-20T00:36:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-20T00:36:14+00:00</t>
+          <t>2026-06-21T00:39:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-21T00:39:17+00:00</t>
+          <t>2026-06-22T00:38:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-22T00:38:18+00:00</t>
+          <t>2026-06-23T00:36:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-23T00:36:13+00:00</t>
+          <t>2026-06-24T00:30:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-24T00:30:31+00:00</t>
+          <t>2026-06-25T00:35:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-25T00:35:33+00:00</t>
+          <t>2026-06-26T00:41:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-26T00:41:51+00:00</t>
+          <t>2026-06-27T00:33:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-27T00:33:17+00:00</t>
+          <t>2026-06-28T00:33:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-28T00:33:14+00:00</t>
+          <t>2026-06-29T00:35:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-29T00:35:23+00:00</t>
+          <t>2026-06-30T00:33:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30T00:33:50+00:00</t>
+          <t>2026-07-01T00:38:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-01T00:38:36+00:00</t>
+          <t>2026-07-02T00:33:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-02T00:33:40+00:00</t>
+          <t>2026-07-03T02:05:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-03T02:05:50+00:00</t>
+          <t>2026-07-04T02:03:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-04T02:03:21+00:00</t>
+          <t>2026-07-05T02:11:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-05T02:11:20+00:00</t>
+          <t>2026-07-06T02:16:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-06T02:16:15+00:00</t>
+          <t>2026-07-07T02:11:33+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-07T02:11:33+00:00</t>
+          <t>2026-07-08T01:53:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-08T01:53:09+00:00</t>
+          <t>2026-07-09T02:06:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-09T02:06:11+00:00</t>
+          <t>2026-07-10T02:04:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-10T02:04:44+00:00</t>
+          <t>2026-07-11T01:51:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-11T01:51:22+00:00</t>
+          <t>2026-07-12T01:54:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-12T01:54:07+00:00</t>
+          <t>2026-07-13T01:56:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-13T01:56:44+00:00</t>
+          <t>2026-07-14T01:43:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-14T01:43:48+00:00</t>
+          <t>2026-07-15T01:29:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-15T01:29:25+00:00</t>
+          <t>2026-07-16T01:50:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-16T01:50:01+00:00</t>
+          <t>2026-07-17T01:53:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-17T01:53:31+00:00</t>
+          <t>2026-07-18T01:44:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-18T01:44:01+00:00</t>
+          <t>2026-07-19T01:52:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-19T01:52:05+00:00</t>
+          <t>2026-07-20T03:25:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-20T03:25:58+00:00</t>
+          <t>2026-07-21T01:55:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-21T01:55:43+00:00</t>
+          <t>2026-07-22T01:50:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-22T01:50:58+00:00</t>
+          <t>2026-07-23T01:59:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-23T01:59:39+00:00</t>
+          <t>2026-07-24T01:54:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-24T01:54:58+00:00</t>
+          <t>2026-07-25T01:53:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-25T01:53:37+00:00</t>
+          <t>2026-07-26T01:57:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-26T01:57:21+00:00</t>
+          <t>2026-07-27T02:07:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-27T02:07:49+00:00</t>
+          <t>2026-07-28T01:47:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-28T01:47:19+00:00</t>
+          <t>2026-07-29T01:49:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-29T01:49:09+00:00</t>
+          <t>2026-07-30T01:32:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-30T01:32:41+00:00</t>
+          <t>2026-07-31T01:58:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31T01:58:49+00:00</t>
+          <t>2026-08-01T02:01:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-01T02:01:02+00:00</t>
+          <t>2026-08-02T01:55:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-02T01:55:12+00:00</t>
+          <t>2026-08-03T01:57:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-03T01:57:53+00:00</t>
+          <t>2026-08-04T01:44:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-04T01:44:59+00:00</t>
+          <t>2026-08-05T01:46:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-05T01:46:13+00:00</t>
+          <t>2026-08-06T01:46:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-06T01:46:40+00:00</t>
+          <t>2026-08-07T02:11:08+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-07T02:11:08+00:00</t>
+          <t>2026-08-08T00:58:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-08T00:58:06+00:00</t>
+          <t>2026-08-09T01:02:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-09T01:02:21+00:00</t>
+          <t>2026-08-10T01:04:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-10T01:04:32+00:00</t>
+          <t>2026-08-11T01:02:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-11T01:02:51+00:00</t>
+          <t>2026-08-12T01:10:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-12T01:10:18+00:00</t>
+          <t>2026-08-13T01:12:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-13T01:12:43+00:00</t>
+          <t>2026-08-14T01:10:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-14T01:10:39+00:00</t>
+          <t>2026-08-15T00:44:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-15T00:44:15+00:00</t>
+          <t>2026-08-16T00:45:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-16T00:45:11+00:00</t>
+          <t>2026-08-17T00:43:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T00:43:29+00:00</t>
+          <t>2026-08-17T06:43:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:43:43+00:00</t>
+          <t>2026-08-17T06:55:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T06:55:56+00:00</t>
+          <t>2026-08-17T07:43:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$E$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Data'!$A$1:$E$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>https://images.transparencycdn.org/images/CPI2024-Results-and-trends.xlsx</t>
+          <t>https://images.transparencycdn.org/images/CPI2025_Results.xlsx</t>
         </is>
       </c>
     </row>
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T07:43:25+00:00</t>
+          <t>2026-08-17T08:00:53+00:00</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -533,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -687,16 +687,16 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -705,12 +705,12 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -737,12 +737,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -751,12 +751,12 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
@@ -783,17 +783,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -825,30 +825,30 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
@@ -871,21 +871,21 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
@@ -894,44 +894,44 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
@@ -944,21 +944,21 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19">
@@ -981,7 +981,7 @@
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20">
@@ -990,21 +990,21 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Seychelles</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -1013,35 +1013,35 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1050,12 +1050,12 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
@@ -1078,44 +1078,44 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E25" s="5" t="n">
@@ -1124,71 +1124,71 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Seychelles</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>TWN</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>TWN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -1216,16 +1216,16 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -1234,26 +1234,26 @@
         </is>
       </c>
       <c r="E30" s="5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">
@@ -1262,16 +1262,16 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>Korea, South</t>
+          <t>Brunei Darussalam</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -1280,12 +1280,12 @@
         </is>
       </c>
       <c r="E32" s="5" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
@@ -1308,21 +1308,21 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Korea, South</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E34" s="5" t="n">
@@ -1331,7 +1331,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
@@ -1377,44 +1377,44 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>DMA</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>DMA</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -1423,7 +1423,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
@@ -1441,26 +1441,26 @@
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
@@ -1492,44 +1492,44 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E42" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -1538,16 +1538,16 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Rwanda</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -1556,21 +1556,21 @@
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -1579,26 +1579,26 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>Rwanda</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
@@ -1634,17 +1634,17 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
@@ -1676,16 +1676,16 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -1694,12 +1694,12 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
@@ -1722,21 +1722,21 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -1763,26 +1763,26 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
@@ -1791,48 +1791,48 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="57">
@@ -1841,40 +1841,40 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Mauritius</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -1883,21 +1883,21 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>VUT</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -1906,44 +1906,44 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -1952,16 +1952,16 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Mauritius</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -1970,12 +1970,12 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
@@ -2002,17 +2002,17 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
@@ -2025,17 +2025,17 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -2048,17 +2048,17 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -2071,17 +2071,17 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -2136,16 +2136,16 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -2154,21 +2154,21 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>Côte d'Ivoire</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -2182,21 +2182,21 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -2205,16 +2205,16 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>KSV</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>China</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>WE/EU</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
@@ -2324,17 +2324,17 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
@@ -2370,17 +2370,17 @@
       </c>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>KSV</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -2412,16 +2412,16 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -2430,26 +2430,26 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -2458,21 +2458,21 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
@@ -2481,16 +2481,16 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -2499,21 +2499,21 @@
         </is>
       </c>
       <c r="E85" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -2522,44 +2522,44 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>Tanzania</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -2568,26 +2568,26 @@
         </is>
       </c>
       <c r="E88" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>WE/EU</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -2596,7 +2596,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
@@ -2619,21 +2619,21 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Tanzania</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
@@ -2642,44 +2642,44 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -2688,21 +2688,21 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>MDV</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -2711,16 +2711,16 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -2734,21 +2734,21 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>Zambia</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>ZMB</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Ethiopia</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -2784,17 +2784,17 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>MDV</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="B101" s="5" t="inlineStr">
         <is>
-          <t>Ethiopia</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
@@ -2922,17 +2922,17 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Zambia</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
@@ -2945,12 +2945,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -2964,30 +2964,30 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="108">
@@ -3014,21 +3014,21 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="109">
@@ -3037,40 +3037,40 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>Malawi</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -3079,21 +3079,21 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
@@ -3102,21 +3102,21 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
@@ -3125,16 +3125,16 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -3148,21 +3148,21 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B114" s="5" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Malawi</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
@@ -3171,67 +3171,67 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B115" s="5" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="n">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
@@ -3240,21 +3240,21 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -3263,21 +3263,21 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
@@ -3286,16 +3286,16 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -3309,16 +3309,16 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Angola</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>AGO</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -3327,26 +3327,26 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>Angola</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>AGO</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -3355,21 +3355,21 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
@@ -3378,16 +3378,16 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>Kenya</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -3401,39 +3401,39 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="5" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Djibouti</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -3442,44 +3442,44 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="5" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B127" s="5" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="5" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B128" s="5" t="inlineStr">
         <is>
-          <t>Djibouti</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -3493,21 +3493,21 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B129" s="5" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
@@ -3516,21 +3516,21 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B130" s="5" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Kenya</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -3608,48 +3608,48 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="5" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="136">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -3672,67 +3672,67 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>IRQ</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B139" s="5" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -3741,90 +3741,90 @@
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="5" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B140" s="5" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="5" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B141" s="5" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="5" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B142" s="5" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>IRQ</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B143" s="5" t="inlineStr">
         <is>
-          <t>Madagascar</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
@@ -3838,16 +3838,16 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B144" s="5" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
@@ -3861,16 +3861,16 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B145" s="5" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
@@ -3884,21 +3884,21 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B146" s="5" t="inlineStr">
         <is>
-          <t>Uganda</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
@@ -3907,62 +3907,62 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B147" s="5" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="5" t="n">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B148" s="5" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="5" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>Mozambique</t>
+          <t>Madagascar</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
@@ -3976,16 +3976,16 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>Central African Republic</t>
+          <t>Uganda</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="D150" s="5" t="inlineStr">
@@ -3994,26 +3994,26 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="5" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="D151" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E151" s="5" t="n">
@@ -4022,67 +4022,67 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Central African Republic</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="D152" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E152" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="5" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B153" s="5" t="inlineStr">
         <is>
-          <t>Congo</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="C153" s="5" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="D153" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B154" s="5" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Congo</t>
         </is>
       </c>
       <c r="C154" s="5" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="D154" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E154" s="5" t="n">
@@ -4091,53 +4091,53 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B155" s="5" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="C155" s="5" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="D155" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E155" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="D156" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E156" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="5" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
@@ -4155,26 +4155,26 @@
         </is>
       </c>
       <c r="E157" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="5" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Chad</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="D158" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
@@ -4183,62 +4183,62 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="D159" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E159" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="5" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>Chad</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="D160" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E160" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="5" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>Comoros</t>
+          <t>Zimbabwe</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="D161" s="5" t="inlineStr">
@@ -4247,16 +4247,16 @@
         </is>
       </c>
       <c r="E161" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="5" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Guinea Bissau</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
@@ -4275,16 +4275,16 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>Zimbabwe</t>
+          <t>Mozambique</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>ZWE</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
@@ -4302,17 +4302,17 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>Democratic Republic of the Congo</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E164" s="5" t="n">
@@ -4321,90 +4321,90 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Comoros</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E165" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="5" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E166" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="5" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>Burundi</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E167" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Burundi</t>
         </is>
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
         <is>
-          <t>ECA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E168" s="5" t="n">
@@ -4413,39 +4413,39 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>ECA</t>
         </is>
       </c>
       <c r="E169" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="5" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>MMR</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -4459,48 +4459,48 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>Korea, North</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>PRK</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E171" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>MMR</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E172" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173">
@@ -4509,113 +4509,113 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="5" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Korea, North</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>PRK</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>AP</t>
         </is>
       </c>
       <c r="E174" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="5" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>ERI</t>
+          <t>SYR</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E175" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="5" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>AME</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>YEM</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E177" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="178">
@@ -4624,67 +4624,67 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Eritrea</t>
         </is>
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>SYR</t>
+          <t>ERI</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
         <is>
-          <t>MENA</t>
+          <t>SSA</t>
         </is>
       </c>
       <c r="E178" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="5" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
         <is>
-          <t>AME</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E179" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="5" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>Somalia</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>YEM</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
         <is>
-          <t>SSA</t>
+          <t>MENA</t>
         </is>
       </c>
       <c r="E180" s="5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181">
@@ -4693,25 +4693,71 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
+          <t>Venezuela</t>
+        </is>
+      </c>
+      <c r="C181" s="5" t="inlineStr">
+        <is>
+          <t>VEN</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="inlineStr">
+        <is>
+          <t>AME</t>
+        </is>
+      </c>
+      <c r="E181" s="5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="5" t="inlineStr">
+        <is>
+          <t>Somalia</t>
+        </is>
+      </c>
+      <c r="C182" s="5" t="inlineStr">
+        <is>
+          <t>SOM</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="E182" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="5" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" s="5" t="inlineStr">
+        <is>
           <t>South Sudan</t>
         </is>
       </c>
-      <c r="C181" s="5" t="inlineStr">
+      <c r="C183" s="5" t="inlineStr">
         <is>
           <t>SSD</t>
         </is>
       </c>
-      <c r="D181" s="5" t="inlineStr">
-        <is>
-          <t>SSA</t>
-        </is>
-      </c>
-      <c r="E181" s="5" t="n">
-        <v>8</v>
+      <c r="D183" s="5" t="inlineStr">
+        <is>
+          <t>SSA</t>
+        </is>
+      </c>
+      <c r="E183" s="5" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E181"/>
+  <autoFilter ref="A1:E183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:00:53+00:00</t>
+          <t>2026-08-17T08:14:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:14:19+00:00</t>
+          <t>2026-08-17T08:29:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T08:29:36+00:00</t>
+          <t>2026-08-17T09:21:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:21:54+00:00</t>
+          <t>2026-08-17T09:27:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T09:27:20+00:00</t>
+          <t>2026-08-17T10:46:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T10:46:01+00:00</t>
+          <t>2026-08-17T12:52:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T12:52:27+00:00</t>
+          <t>2026-08-17T23:14:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-17T23:14:59+00:00</t>
+          <t>2026-08-18T05:53:28+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T05:53:28+00:00</t>
+          <t>2026-08-18T23:15:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-18T23:15:09+00:00</t>
+          <t>2026-08-19T23:15:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-19T23:15:51+00:00</t>
+          <t>2026-08-20T23:18:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-20T23:18:25+00:00</t>
+          <t>2026-08-21T23:15:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-21T23:15:53+00:00</t>
+          <t>2026-08-22T23:13:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-22T23:13:45+00:00</t>
+          <t>2026-08-23T23:13:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-23T23:13:17+00:00</t>
+          <t>2026-08-24T23:16:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-24T23:16:24+00:00</t>
+          <t>2026-08-25T23:18:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-25T23:18:13+00:00</t>
+          <t>2026-08-27T04:10:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-27T04:10:19+00:00</t>
+          <t>2026-08-28T06:26:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28T06:26:55+00:00</t>
+          <t>2026-08-29T03:59:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-29T03:59:12+00:00</t>
+          <t>2026-08-30T00:56:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-30T00:56:46+00:00</t>
+          <t>2026-08-31T01:01:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-31T01:01:25+00:00</t>
+          <t>2026-09-01T01:31:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01T01:31:55+00:00</t>
+          <t>2026-09-02T00:41:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02T00:41:50+00:00</t>
+          <t>2026-09-03T00:53:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03T00:53:40+00:00</t>
+          <t>2026-09-04T00:33:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-04T00:33:50+00:00</t>
+          <t>2026-09-05T00:31:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-05T00:31:26+00:00</t>
+          <t>2026-09-06T00:24:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-06T00:24:19+00:00</t>
+          <t>2026-09-07T00:31:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T00:31:34+00:00</t>
+          <t>2026-09-07T07:49:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T07:49:53+00:00</t>
+          <t>2026-09-07T09:43:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T09:43:25+00:00</t>
+          <t>2026-09-07T11:03:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-07T11:03:04+00:00</t>
+          <t>2026-09-08T00:50:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-08T00:50:25+00:00</t>
+          <t>2026-09-09T00:54:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T00:54:14+00:00</t>
+          <t>2026-09-09T01:45:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T01:45:46+00:00</t>
+          <t>2026-09-09T02:38:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-09T02:38:44+00:00</t>
+          <t>2026-09-10T00:44:23+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-10T00:44:23+00:00</t>
+          <t>2026-09-11T00:42:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-11T00:42:40+00:00</t>
+          <t>2026-09-12T00:50:40+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/ti-cpi.xlsx
+++ b/public/downloads/ti-cpi.xlsx
@@ -502,7 +502,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-12T00:50:40+00:00</t>
+          <t>2026-09-13T00:31:17+00:00</t>
         </is>
       </c>
     </row>
